--- a/research/traditional_assets/database/data/oman/oman_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,41 +587,47 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D2">
+        <v>-0.01045</v>
+      </c>
+      <c r="E2">
+        <v>-0.0353</v>
+      </c>
       <c r="G2">
-        <v>0.2801470588235294</v>
+        <v>0.1183016105417277</v>
       </c>
       <c r="H2">
-        <v>0.2801470588235294</v>
+        <v>0.1183016105417277</v>
       </c>
       <c r="I2">
-        <v>-0.1073529411764706</v>
+        <v>0.08272327964860908</v>
       </c>
       <c r="J2">
-        <v>-0.1073529411764706</v>
+        <v>0.0767493830766777</v>
       </c>
       <c r="K2">
-        <v>-1.46</v>
+        <v>4.56</v>
       </c>
       <c r="L2">
-        <v>-0.1073529411764706</v>
+        <v>0.06676427525622255</v>
       </c>
       <c r="M2">
-        <v>1.3</v>
+        <v>6.49</v>
       </c>
       <c r="N2">
-        <v>0.05439330543933055</v>
+        <v>0.0437626432906271</v>
       </c>
       <c r="O2">
-        <v>-0.8904109589041096</v>
+        <v>1.423245614035088</v>
       </c>
       <c r="P2">
-        <v>1.3</v>
+        <v>6.49</v>
       </c>
       <c r="Q2">
-        <v>0.05439330543933055</v>
+        <v>0.0437626432906271</v>
       </c>
       <c r="R2">
-        <v>-0.8904109589041096</v>
+        <v>1.423245614035088</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -630,67 +636,70 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>6.12</v>
+        <v>7.64</v>
       </c>
       <c r="V2">
-        <v>0.2560669456066946</v>
+        <v>0.05151719487525286</v>
       </c>
       <c r="W2">
-        <v>-0.03782383419689119</v>
+        <v>0.001562476687803058</v>
       </c>
       <c r="X2">
-        <v>0.07697577764364623</v>
+        <v>0.1231773548421465</v>
       </c>
       <c r="Y2">
-        <v>-0.1147996118405374</v>
+        <v>-0.1216148781543434</v>
       </c>
       <c r="Z2">
-        <v>0.4398447606727037</v>
+        <v>0.7609180035650625</v>
       </c>
       <c r="AA2">
-        <v>-0.04721862871927555</v>
+        <v>0.02211097898015715</v>
       </c>
       <c r="AB2">
-        <v>0.07697577764364623</v>
+        <v>0.1229201206393559</v>
       </c>
       <c r="AC2">
-        <v>-0.1241944063629218</v>
+        <v>-0.1008091416591987</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG2">
-        <v>-6.12</v>
+        <v>-6.3</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.008954824913124833</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>0.00948068487335503</v>
       </c>
       <c r="AJ2">
-        <v>-0.344206974128234</v>
+        <v>-0.04436619718309859</v>
       </c>
       <c r="AK2">
-        <v>-0.1901802361715351</v>
+        <v>-0.04712041884816754</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AN2">
-        <v>-0</v>
+        <v>0.2042682926829268</v>
       </c>
       <c r="AP2">
-        <v>4.744186046511627</v>
+        <v>-0.9603658536585364</v>
+      </c>
+      <c r="AQ2">
+        <v>-80.71428571428569</v>
       </c>
     </row>
     <row r="3">
@@ -701,118 +710,249 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Al Ahlia Insurance Company SAOG (MSM:AINS)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>-0.0709</v>
+      </c>
+      <c r="E3">
+        <v>-0.0353</v>
+      </c>
+      <c r="G3">
+        <v>0.2802690582959641</v>
+      </c>
+      <c r="H3">
+        <v>0.2802690582959641</v>
+      </c>
+      <c r="I3">
+        <v>0.1816143497757848</v>
+      </c>
+      <c r="J3">
+        <v>0.15538363585468</v>
+      </c>
+      <c r="K3">
+        <v>6.99</v>
+      </c>
+      <c r="L3">
+        <v>0.1567264573991031</v>
+      </c>
+      <c r="M3">
+        <v>6.49</v>
+      </c>
+      <c r="N3">
+        <v>0.05481418918918919</v>
+      </c>
+      <c r="O3">
+        <v>0.9284692417739628</v>
+      </c>
+      <c r="P3">
+        <v>6.49</v>
+      </c>
+      <c r="Q3">
+        <v>0.05481418918918919</v>
+      </c>
+      <c r="R3">
+        <v>0.9284692417739628</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>2.5</v>
+      </c>
+      <c r="V3">
+        <v>0.02111486486486486</v>
+      </c>
+      <c r="W3">
+        <v>0.06657142857142857</v>
+      </c>
+      <c r="X3">
+        <v>0.1235812642776119</v>
+      </c>
+      <c r="Y3">
+        <v>-0.05700983570618333</v>
+      </c>
+      <c r="Z3">
+        <v>0.7745745050364711</v>
+      </c>
+      <c r="AA3">
+        <v>0.120356202832906</v>
+      </c>
+      <c r="AB3">
+        <v>0.1230667958720307</v>
+      </c>
+      <c r="AC3">
+        <v>-0.002710593039124728</v>
+      </c>
+      <c r="AD3">
+        <v>1.34</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>1.34</v>
+      </c>
+      <c r="AG3">
+        <v>-1.16</v>
+      </c>
+      <c r="AH3">
+        <v>0.01119091364623351</v>
+      </c>
+      <c r="AI3">
+        <v>0.01257743570489957</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.009894234049812349</v>
+      </c>
+      <c r="AK3">
+        <v>-0.01114955786236063</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="AN3">
+        <v>0.1519274376417234</v>
+      </c>
+      <c r="AP3">
+        <v>-0.1315192743764172</v>
+      </c>
+      <c r="AQ3">
+        <v>-115.7142857142857</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Vision Insurance SAOG (MSM:VISN)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="G3">
-        <v>0.2801470588235294</v>
-      </c>
-      <c r="H3">
-        <v>0.2801470588235294</v>
-      </c>
-      <c r="I3">
-        <v>-0.1073529411764706</v>
-      </c>
-      <c r="J3">
-        <v>-0.1073529411764706</v>
-      </c>
-      <c r="K3">
-        <v>-1.46</v>
-      </c>
-      <c r="L3">
-        <v>-0.1073529411764706</v>
-      </c>
-      <c r="M3">
-        <v>1.3</v>
-      </c>
-      <c r="N3">
-        <v>0.05439330543933055</v>
-      </c>
-      <c r="O3">
-        <v>-0.8904109589041096</v>
-      </c>
-      <c r="P3">
-        <v>1.3</v>
-      </c>
-      <c r="Q3">
-        <v>0.05439330543933055</v>
-      </c>
-      <c r="R3">
-        <v>-0.8904109589041096</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>6.12</v>
-      </c>
-      <c r="V3">
-        <v>0.2560669456066946</v>
-      </c>
-      <c r="W3">
-        <v>-0.03782383419689119</v>
-      </c>
-      <c r="X3">
-        <v>0.07697577764364623</v>
-      </c>
-      <c r="Y3">
-        <v>-0.1147996118405374</v>
-      </c>
-      <c r="Z3">
-        <v>0.4398447606727037</v>
-      </c>
-      <c r="AA3">
-        <v>-0.04721862871927555</v>
-      </c>
-      <c r="AB3">
-        <v>0.07697577764364623</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1241944063629218</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
-      <c r="AG3">
-        <v>-6.12</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AI3">
-        <v>0</v>
-      </c>
-      <c r="AJ3">
-        <v>-0.344206974128234</v>
-      </c>
-      <c r="AK3">
-        <v>-0.1901802361715351</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
+      <c r="D4">
+        <v>0.05</v>
+      </c>
+      <c r="G4">
+        <v>-0.1864978902953587</v>
+      </c>
+      <c r="H4">
+        <v>-0.1864978902953587</v>
+      </c>
+      <c r="I4">
+        <v>-0.1033755274261604</v>
+      </c>
+      <c r="J4">
+        <v>-0.1033755274261604</v>
+      </c>
+      <c r="K4">
+        <v>-2.43</v>
+      </c>
+      <c r="L4">
+        <v>-0.1025316455696203</v>
+      </c>
+      <c r="M4">
         <v>-0</v>
       </c>
-      <c r="AP3">
-        <v>4.744186046511627</v>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>5.14</v>
+      </c>
+      <c r="V4">
+        <v>0.1719063545150502</v>
+      </c>
+      <c r="W4">
+        <v>-0.06344647519582246</v>
+      </c>
+      <c r="X4">
+        <v>0.1227734454066811</v>
+      </c>
+      <c r="Y4">
+        <v>-0.1862199206025035</v>
+      </c>
+      <c r="Z4">
+        <v>0.7364822871348664</v>
+      </c>
+      <c r="AA4">
+        <v>-0.07613424487259168</v>
+      </c>
+      <c r="AB4">
+        <v>0.1227734454066811</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1989076902792727</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>-5.14</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.2075928917609047</v>
+      </c>
+      <c r="AK4">
+        <v>-0.1732973701955496</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>-0</v>
+      </c>
+      <c r="AP4">
+        <v>2.274336283185841</v>
       </c>
     </row>
   </sheetData>
